--- a/extenbooks/ES1401.xlsx
+++ b/extenbooks/ES1401.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 5</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -982,174 +982,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1401-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohun 2005 CJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1401 — Exploitation Rate — Mohun 2005</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Mohun 2005 CJE)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1401 — Exploitation Rate — Mohun 2005</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1948, 1989]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Chapter**: External study (Mohun 2005 CJE)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1948, 1989]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: ratio</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mohun's alternative-classification exploitation rate, applying a narrower productive/unproductive partition than Shaikh &amp; Tonak. The cross-validation series — used in V09 internally.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mohun's alternative-classification exploitation rate, applying a narrower productive/unproductive partition than Shaikh &amp; Tonak. The cross-validation series — used in V09 internally.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Mohun_mohun_exploitation_rates_1948_1989_CORRECTED.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1401_exploitation_rate_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1401_exploitation_rate_mohun2005.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Mohun_mohun_exploitation_rates_1948_1989_CORRECTED.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1401_exploitation_rate_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1401_exploitation_rate_mohun2005.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Mohun_mohun_exploitation_rates_1948_1989_CORRECTED.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1401 -&gt; data/intermediate/ES1401.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1401 -&gt; data/final/ES1401.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1158,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1401 -&gt; data/intermediate/validation/ES1401.json</t>
+          <t>data/source/external_studies/Mohun_mohun_exploitation_rates_1948_1989_CORRECTED.csv</t>
         </is>
       </c>
     </row>
@@ -1165,53 +1166,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1401 -&gt; data/intermediate/ES1401.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1401 -&gt; data/final/ES1401.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1401 -&gt; data/intermediate/validation/ES1401.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On Measuring the Wealth of Nations: The U.S. Economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On Measuring the Wealth of Nations: The U.S. Economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1228,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1256,163 +1281,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rate of surplus value = (aggregate money value added - productive wages) / productive wages = S/V, using Mohun's SM approximation procedures. Mohun (2005) critiques the ST (1994) approximation methods and proposes superior SM alternatives. The exploitation rate under Mohun's classification is lower than ST's because Mohun applies a broader productive sector boundary — his Information sector is treated as entirely productive, and retail eating/drinking places are also classified productive. The SM approximation for services uses division-level BLS production worker ratios weighted against the aggregate Services BLS ratio, rather than ST's GDP-contribution weighting.</t>
+          <t>The paper finds that the compromises made by Shaikh and Tonak because of data unavailability are unreliable, and that better approximations are possible. On this latter basis, the Shaikh and Tonak methodology can be used to provide the labour and wage estimates needed for empirical investigations in the surplus-based tradition.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 2-4; full_transcription.md Fig 4 discussion</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>benchmark_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SM estimates from Figure 4: average rate of surplus value 1964-1982 = 1.97; value in 2001 = 3.00, representing a +52% increase over the 1964-1982 average. ST estimates for same period: average 1964-1982 = 1.71; 2001 = 2.22 (+29.8%). ST captures only 57% of the actual increase identified by the SM method.</t>
+          <t>SM: From ~1.97 (1964-82 average) to 3.00 (2001) = +52%. ST shows +29.8% increase 1964-82 to 2001. ST captures only 57% of actual increase.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohun_2005, Fig 4; full_transcription.md Section 4</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>approximation_performance</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>For services sector wages 1988-2001 (where benchmark is available): ST approximation averages 172% of benchmark (sd 3.71), a massive 72% overestimate. SM approximation averages 101.5% of benchmark (sd 1.08), a 1.5% overestimate. For services employment: ST averages 91.2% of benchmark (sd 1.26); SM averages 98.6% (sd 0.23). The large ST wage overestimate flows directly into a systematic understatement of the exploitation rate, because overestimated productive wages yield an artificially compressed surplus/variable-capital ratio.</t>
+          <t>Wages: ST: 172% of benchmark (sd 3.71) — 72% OVERESTIMATE; SM: 101.5% of benchmark (sd 1.08) — 1.5% overestimate. Numbers: ST: 91.2% of benchmark (sd 1.26) — 8.8% underestimate; SM: 98.6% of benchmark (sd 0.23) — 1.4% underestimate.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 3.1; full_transcription.md Tables 2-3</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>structural_break</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Both ST and SM methods identify a major structural break at the beginning of the 1980s. Mohun states: 'While both ST and SM estimates identify that something dramatic happened in the US economy at the beginning of the 1980s, marking a major and lasting change with what went before, the ST method of approximation, compared with the SM method, substantially understates its impact on the rate of surplus value.' This corresponds to the Volcker interest rate shock and the onset of neoliberal restructuring.</t>
+          <t>While both ST and SM estimates identify that something dramatic happened in the US economy at the beginning of the 1980s, marking a major and lasting change with what went before, the ST method of approximation, compared with the SM method, substantially understates its impact on the rate of surplus value.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 4; full_transcription.md Conclusion</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>classification_boundary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2005) fully accepts ST's conceptual framework and SIC classification — he does NOT challenge which sectors are productive. His critique is solely about the approximation procedures used to calculate productive labor quantities and wages within that framework. The exploitation rate difference between ST and Mohun (ES1404 ratio ≈ 1.61) arises from classification differences introduced in the 2013 paper, not from this 2005 paper.</t>
+          <t>Does NOT address: Whether productive/unproductive labor distinction is meaningful; Whether specific sectors should be classified as productive. Accepts: ST's conceptual framework and SIC classification throughout. Questions: HOW the results are obtained, not WHAT they show.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 1 Introduction; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_period</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coverage: 1964-2001 (38 years). Data sources: NIPA (BEA), broken down by industrial division under 1972 SIC (1964-87) and 1987 SIC (1987-2001); BLS Employment, Hours and Earnings for production worker ratios and wages. SIC revision from 1972 to 1987 base is 'not very significant at aggregation level of this paper.'</t>
+          <t>1964-87: 1972 SIC; 1987-2001: 1987 SIC (second entry for 1987 uses 1987 SIC). At the level of aggregation of this paper, the differences resulting from the change in SIC are small.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 1; Appendix A.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rate of surplus value = (aggregate money value added - productive wages) / productive wages = S/V, using Mohun's SM approximation procedures. Mohun (2005) critiques the ST (1994) approximation methods and proposes superior SM alternatives. The exploitation rate under Mohun's classification is lower than ST's because Mohun applies a broader productive sector boundary — his Information sector is treated as entirely productive, and retail eating/drinking places are also classified productive. The SM approximation for services uses division-level BLS production worker ratios weighted against the aggregate Services BLS ratio, rather than ST's GDP-contribution weighting.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 2-4; full_transcription.md Fig 4 discussion</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>benchmark_values</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Exploitation rate under Mohun's SM approximation procedures. Period 1964-2001. Average 1964-1982 = 1.97, rising to 3.00 in 2001 (+52%). ST method understates post-1980 rise, capturing only 57% of actual increase. Loaded from Mohun 2005 Table 2 via L15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>SM estimates from Figure 4: average rate of surplus value 1964-1982 = 1.97; value in 2001 = 3.00, representing a +52% increase over the 1964-1982 average. ST estimates for same period: average 1964-1982 = 1.71; 2001 = 2.22 (+29.8%). ST captures only 57% of the actual increase identified by the SM method.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Fig 4; full_transcription.md Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>approximation_performance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>For services sector wages 1988-2001 (where benchmark is available): ST approximation averages 172% of benchmark (sd 3.71), a massive 72% overestimate. SM approximation averages 101.5% of benchmark (sd 1.08), a 1.5% overestimate. For services employment: ST averages 91.2% of benchmark (sd 1.26); SM averages 98.6% (sd 0.23). The large ST wage overestimate flows directly into a systematic understatement of the exploitation rate, because overestimated productive wages yield an artificially compressed surplus/variable-capital ratio.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 3.1; full_transcription.md Tables 2-3</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>structural_break</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Both ST and SM methods identify a major structural break at the beginning of the 1980s. Mohun states: 'While both ST and SM estimates identify that something dramatic happened in the US economy at the beginning of the 1980s, marking a major and lasting change with what went before, the ST method of approximation, compared with the SM method, substantially understates its impact on the rate of surplus value.' This corresponds to the Volcker interest rate shock and the onset of neoliberal restructuring.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 4; full_transcription.md Conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>classification_boundary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mohun (2005) fully accepts ST's conceptual framework and SIC classification — he does NOT challenge which sectors are productive. His critique is solely about the approximation procedures used to calculate productive labor quantities and wages within that framework. The exploitation rate difference between ST and Mohun (ES1404 ratio ≈ 1.61) arises from classification differences introduced in the 2013 paper, not from this 2005 paper.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 1 Introduction; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>data_period</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Coverage: 1964-2001 (38 years). Data sources: NIPA (BEA), broken down by industrial division under 1972 SIC (1964-87) and 1987 SIC (1987-2001); BLS Employment, Hours and Earnings for production worker ratios and wages. SIC revision from 1972 to 1987 base is 'not very significant at aggregation level of this paper.'</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 1; Appendix A.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Exploitation rate under Mohun's SM approximation procedures. Period 1964-2001. Average 1964-1982 = 1.97, rising to 3.00 in 2001 (+52%). ST method understates post-1980 rise, capturing only 57% of actual increase. Loaded from Mohun 2005 Table 2 via L15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Data ends 2001; no extension to later years under this paper's methodology</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SIC revision 1972-to-1987 at 1987 boundary introduces minor discontinuity (assessed as small by Mohun)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SM approximation still averages 101.5% of benchmark for wages — small systematic overestimate persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ES1402</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1507,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1403</t>
+          <t>Data ends 2001; no extension to later years under this paper's methodology</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1515,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1404</t>
+          <t>SIC revision 1972-to-1987 at 1987 boundary introduces minor discontinuity (assessed as small by Mohun)</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1523,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S506</t>
+          <t>SM approximation still averages 101.5% of benchmark for wages — small systematic overestimate persists</t>
         </is>
       </c>
     </row>
@@ -1444,29 +1531,69 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1483,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1546,7 +1673,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1694,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 1.6666}</t>
         </is>
       </c>
     </row>
@@ -1592,6 +1719,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
